--- a/academias/Laboratorio Clínico - Estadisticos 20232.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20232.xlsx
@@ -683,25 +683,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -820,25 +820,25 @@
         <v>152</v>
       </c>
       <c r="E10">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>73</v>
+        <v>94.7</v>
       </c>
       <c r="H10" s="1">
-        <v>27</v>
+        <v>5.3</v>
       </c>
       <c r="I10" s="2">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1499,25 +1499,25 @@
         <v>757</v>
       </c>
       <c r="E30">
-        <v>649</v>
+        <v>682</v>
       </c>
       <c r="F30">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="G30" s="1">
-        <v>85.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>14.3</v>
+        <v>9.9</v>
       </c>
       <c r="I30" s="2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1585,25 +1585,25 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1620,25 +1620,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>30.8</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1655,25 +1655,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1687,25 +1687,25 @@
         <v>116</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F5">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>26.7</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1722,25 +1722,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1757,25 +1757,25 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F7">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1792,25 +1792,25 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1827,25 +1827,25 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J9">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1859,25 +1859,25 @@
         <v>152</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="F10">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>92.8</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>7.2</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1894,25 +1894,25 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1929,25 +1929,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>9.4</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1961,25 +1961,25 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F13">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>80.3</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>19.7</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1996,25 +1996,25 @@
         <v>42</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2031,25 +2031,25 @@
         <v>42</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F15">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2063,25 +2063,25 @@
         <v>84</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F16">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>4.8</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J16">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2098,25 +2098,25 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>12.9</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2133,25 +2133,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>3.1</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2165,25 +2165,25 @@
         <v>63</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F19">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2200,25 +2200,25 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J20">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2235,25 +2235,25 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J21">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2270,25 +2270,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2302,25 +2302,25 @@
         <v>91</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F23">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>81.3</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>18.7</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J23">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2337,25 +2337,25 @@
         <v>42</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F24">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>2.4</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J24">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2372,25 +2372,25 @@
         <v>37</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F25">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J25">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2407,25 +2407,25 @@
         <v>37</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F26">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J26">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2442,25 +2442,25 @@
         <v>37</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F27">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2477,25 +2477,25 @@
         <v>37</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J28">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2509,25 +2509,25 @@
         <v>190</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="F29">
-        <v>190</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="I29" s="2">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="J29">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2538,25 +2538,25 @@
         <v>757</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="F30">
-        <v>757</v>
+        <v>81</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I30" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J30">
-        <v>757</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2624,19 +2624,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>82.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="H2" s="1">
-        <v>17.9</v>
+        <v>33.3</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2659,19 +2659,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>84.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="H3" s="1">
-        <v>15.4</v>
+        <v>30.8</v>
       </c>
       <c r="I3" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2694,19 +2694,19 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H4" s="1">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2726,19 +2726,19 @@
         <v>116</v>
       </c>
       <c r="E5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1">
-        <v>81.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H5" s="1">
-        <v>18.1</v>
+        <v>26.7</v>
       </c>
       <c r="I5" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2761,25 +2761,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>84.2</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>15.8</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2831,19 +2831,19 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H8" s="1">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="I8" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2866,19 +2866,19 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H9" s="1">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2898,25 +2898,25 @@
         <v>152</v>
       </c>
       <c r="E10">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>73</v>
+        <v>92.8</v>
       </c>
       <c r="H10" s="1">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="I10" s="2">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2933,19 +2933,19 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>48.3</v>
+        <v>69</v>
       </c>
       <c r="H11" s="1">
-        <v>51.7</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3000,19 +3000,19 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>68.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="H13" s="1">
-        <v>31.1</v>
+        <v>19.7</v>
       </c>
       <c r="I13" s="2">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>42</v>
       </c>
       <c r="E14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H14" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I14" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3070,19 +3070,19 @@
         <v>42</v>
       </c>
       <c r="E15">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H15" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I15" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3102,19 +3102,19 @@
         <v>84</v>
       </c>
       <c r="E16">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H16" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I16" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3137,19 +3137,19 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>74.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>25.8</v>
+        <v>12.9</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3172,19 +3172,19 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H18" s="1">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="I18" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3204,19 +3204,19 @@
         <v>63</v>
       </c>
       <c r="E19">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>84.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>15.9</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3239,19 +3239,19 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>100</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3274,19 +3274,19 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>74.2</v>
+        <v>71</v>
       </c>
       <c r="H21" s="1">
-        <v>25.8</v>
+        <v>29</v>
       </c>
       <c r="I21" s="2">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>19.4</v>
       </c>
       <c r="I22" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>91</v>
       </c>
       <c r="E23">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1">
-        <v>84.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="H23" s="1">
-        <v>15.4</v>
+        <v>18.7</v>
       </c>
       <c r="I23" s="2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>2.4</v>
       </c>
       <c r="I24" s="2">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3577,25 +3577,25 @@
         <v>757</v>
       </c>
       <c r="E30">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="F30">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="G30" s="1">
-        <v>85.7</v>
+        <v>89.3</v>
       </c>
       <c r="H30" s="1">
-        <v>14.3</v>
+        <v>10.7</v>
       </c>
       <c r="I30" s="2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Laboratorio Clínico - Estadisticos 20232.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20232.xlsx
@@ -2212,7 +2212,7 @@
         <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>29</v>
       </c>
       <c r="I21" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>19.4</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>18.7</v>
       </c>
       <c r="I23" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -2550,7 +2550,7 @@
         <v>10.7</v>
       </c>
       <c r="I30" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2624,19 +2624,19 @@
         <v>39</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1">
-        <v>66.7</v>
+        <v>92.3</v>
       </c>
       <c r="H2" s="1">
-        <v>33.3</v>
+        <v>7.7</v>
       </c>
       <c r="I2" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2659,19 +2659,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>69.2</v>
+        <v>92.3</v>
       </c>
       <c r="H3" s="1">
-        <v>30.8</v>
+        <v>7.7</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2694,19 +2694,19 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>84.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>15.8</v>
+        <v>2.6</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2726,19 +2726,19 @@
         <v>116</v>
       </c>
       <c r="E5">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>73.3</v>
+        <v>94</v>
       </c>
       <c r="H5" s="1">
-        <v>26.7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>84.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>15.8</v>
+        <v>2.6</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2796,19 +2796,19 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="H7" s="1">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="I7" s="2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>5.3</v>
       </c>
       <c r="I8" s="2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>5.3</v>
       </c>
       <c r="I9" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2898,19 +2898,19 @@
         <v>152</v>
       </c>
       <c r="E10">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>92.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="I10" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2933,19 +2933,19 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>69</v>
+        <v>86.2</v>
       </c>
       <c r="H11" s="1">
-        <v>31</v>
+        <v>13.8</v>
       </c>
       <c r="I11" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2968,19 +2968,19 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3000,19 +3000,19 @@
         <v>61</v>
       </c>
       <c r="E13">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>80.3</v>
+        <v>91.8</v>
       </c>
       <c r="H13" s="1">
-        <v>19.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3035,19 +3035,19 @@
         <v>42</v>
       </c>
       <c r="E14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I14" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3070,19 +3070,19 @@
         <v>42</v>
       </c>
       <c r="E15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I15" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -3102,19 +3102,19 @@
         <v>84</v>
       </c>
       <c r="E16">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3137,19 +3137,19 @@
         <v>31</v>
       </c>
       <c r="E17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="1">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H17" s="1">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="I17" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
         <v>3.1</v>
       </c>
       <c r="I18" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3204,19 +3204,19 @@
         <v>63</v>
       </c>
       <c r="E19">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>92.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H19" s="1">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="I19" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>19.4</v>
       </c>
       <c r="I22" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3353,7 +3353,7 @@
         <v>18.7</v>
       </c>
       <c r="I23" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>2.4</v>
       </c>
       <c r="I24" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3493,7 +3493,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3528,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3560,7 +3560,7 @@
         <v>0.5</v>
       </c>
       <c r="I29" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3577,16 +3577,16 @@
         <v>757</v>
       </c>
       <c r="E30">
-        <v>676</v>
+        <v>712</v>
       </c>
       <c r="F30">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G30" s="1">
-        <v>89.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H30" s="1">
-        <v>10.7</v>
+        <v>5.9</v>
       </c>
       <c r="I30" s="2">
         <v>8.300000000000001</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20232.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20232.xlsx
@@ -3239,19 +3239,19 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>93.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="H20" s="1">
-        <v>6.9</v>
+        <v>10.3</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -3274,19 +3274,19 @@
         <v>31</v>
       </c>
       <c r="E21">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G21" s="1">
-        <v>71</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>29</v>
+        <v>12.9</v>
       </c>
       <c r="I21" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3309,19 +3309,19 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>80.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="H22" s="1">
-        <v>19.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>91</v>
       </c>
       <c r="E23">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F23">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G23" s="1">
-        <v>81.3</v>
+        <v>89</v>
       </c>
       <c r="H23" s="1">
-        <v>18.7</v>
+        <v>11</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3577,16 +3577,16 @@
         <v>757</v>
       </c>
       <c r="E30">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="F30">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G30" s="1">
-        <v>94.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="H30" s="1">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="I30" s="2">
         <v>8.300000000000001</v>
